--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260819.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260819.xlsx
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>500,459,893</t>
+          <t>291,982,953</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>291,982,953</t>
+          <t>500,459,893</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>65,909,149</t>
+          <t>159,177,229</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>159,177,229</t>
+          <t>65,909,149</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
